--- a/data/项目链接清单.xlsx
+++ b/data/项目链接清单.xlsx
@@ -108,30 +108,33 @@
     <t>按键模块、LED灯模块</t>
   </si>
   <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>A0001</t>
+  </si>
+  <si>
+    <t>51单片机无线恒温箱恒温控制系统 1</t>
+  </si>
+  <si>
+    <t>NRF24L01无线通信模块、温度传感器、继电器模块</t>
+  </si>
+  <si>
+    <t>仿真计价不含NRF24L01无线通信模块：Proteus不便模拟真实无线传输，实物可实现。</t>
+  </si>
+  <si>
+    <t>A0002</t>
+  </si>
+  <si>
+    <t>51单片机垃圾箱自动分类加料机快递物流分拣器系统设计 1</t>
+  </si>
+  <si>
+    <t>红外传感器、颜色识别传感器、电机驱动模块</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
-    <t>A0001</t>
-  </si>
-  <si>
-    <t>51单片机无线恒温箱恒温控制系统</t>
-  </si>
-  <si>
-    <t>NRF24L01无线通信模块、温度传感器、继电器模块</t>
-  </si>
-  <si>
-    <t>仿真计价不含NRF24L01无线通信模块：Proteus不便模拟真实无线传输，实物可实现。</t>
-  </si>
-  <si>
-    <t>A0002</t>
-  </si>
-  <si>
-    <t>51单片机垃圾箱自动分类加料机快递物流分拣器系统设计</t>
-  </si>
-  <si>
-    <t>红外传感器、颜色识别传感器、电机驱动模块</t>
-  </si>
-  <si>
     <t>A0003</t>
   </si>
   <si>
@@ -189,7 +192,7 @@
     <t>A0008</t>
   </si>
   <si>
-    <t>51单片机双机串口排队叫号lcd显示设计</t>
+    <t>51单片机双机串口排队叫号lcd显示设计 1</t>
   </si>
   <si>
     <t>显示与交互</t>
@@ -486,7 +489,7 @@
     <t>C002</t>
   </si>
   <si>
-    <t>51单片机多路温度检测</t>
+    <t>51单片机多路温度检测 1</t>
   </si>
   <si>
     <t>温度传感器、数码管显示模块</t>
@@ -531,9 +534,6 @@
     <t>矩阵键盘、蜂鸣器</t>
   </si>
   <si>
-    <t>否</t>
-  </si>
-  <si>
     <t>C007</t>
   </si>
   <si>
@@ -642,7 +642,7 @@
     <t>C019</t>
   </si>
   <si>
-    <t>51单片机按键数码管</t>
+    <t>51单片机按键数码管 1</t>
   </si>
   <si>
     <t>C020</t>
@@ -876,7 +876,7 @@
     <t>J030</t>
   </si>
   <si>
-    <t>STM32交通灯仿真设计_紧急_可调时间_仿真_代码(讲解+报告)</t>
+    <t>STM32交通灯仿真设计_紧急_可调时间_仿真_代码(讲解+报告) 1</t>
   </si>
   <si>
     <t>STM32</t>
@@ -930,7 +930,7 @@
     <t>L004</t>
   </si>
   <si>
-    <t>51单片机超声波测距带语音播报</t>
+    <t>51单片机超声波测距带语音播报 1</t>
   </si>
   <si>
     <t>超声波测距、音频语音</t>
@@ -1137,7 +1137,7 @@
     <t>L027</t>
   </si>
   <si>
-    <t>51单片机多层电梯(1-16层)运行仿真设计</t>
+    <t>51单片机多层电梯(1-16层)运行仿真设计 1</t>
   </si>
   <si>
     <t>按键模块、步进电机驱动模块、数码管显示模块</t>
@@ -1206,7 +1206,7 @@
     <t>L036</t>
   </si>
   <si>
-    <t>51单片机简易出租车计价器</t>
+    <t>51单片机简易出租车计价器 1</t>
   </si>
   <si>
     <t>霍尔速度传感器、LCD1602显示模块、数码管显示模块</t>
@@ -1827,7 +1827,7 @@
     <t>P05</t>
   </si>
   <si>
-    <t>51单片机的简易计算器_LCD1602显示</t>
+    <t>51单片机的简易计算器_LCD1602显示 1</t>
   </si>
   <si>
     <t>LCD1602显示模块、4×4矩阵键盘、数码管显示模块</t>
@@ -1944,19 +1944,19 @@
     <t>P21</t>
   </si>
   <si>
-    <t>51单片机电子钟闹钟LCD1602显示12-24时制切换</t>
+    <t>51单片机电子钟闹钟LCD1602显示12-24时制切换 1</t>
   </si>
   <si>
     <t>P22</t>
   </si>
   <si>
-    <t>51单片机电子钟闹钟数码管显示12-24时制切换</t>
+    <t>51单片机电子钟闹钟数码管显示12-24时制切换 1</t>
   </si>
   <si>
     <t>P23</t>
   </si>
   <si>
-    <t>51单片机的矩阵按键电子琴</t>
+    <t>51单片机的矩阵按键电子琴 1</t>
   </si>
   <si>
     <t>矩阵键盘、蜂鸣器、按键模块</t>
@@ -1965,13 +1965,13 @@
     <t>P24</t>
   </si>
   <si>
-    <t>51单片机贪吃蛇游戏设计</t>
+    <t>51单片机贪吃蛇游戏设计 1</t>
   </si>
   <si>
     <t>P25</t>
   </si>
   <si>
-    <t>51单片机LCD1602显示广告牌设计</t>
+    <t>51单片机LCD1602显示广告牌设计 1</t>
   </si>
   <si>
     <t>LCD1602显示模块</t>
@@ -1980,25 +1980,25 @@
     <t>P26</t>
   </si>
   <si>
-    <t>51单片机8x8LED点阵广告牌设计</t>
+    <t>51单片机8x8LED点阵广告牌设计 1</t>
   </si>
   <si>
     <t>P27</t>
   </si>
   <si>
-    <t>51单片机双机串口通信LCD1602显示设计</t>
+    <t>51单片机双机串口通信LCD1602显示设计 1</t>
   </si>
   <si>
     <t>P28</t>
   </si>
   <si>
-    <t>51单片机电子钟闹钟日期数码管显示设计</t>
+    <t>51单片机电子钟闹钟日期数码管显示设计 1</t>
   </si>
   <si>
     <t>P29</t>
   </si>
   <si>
-    <t>51单片机模拟风扇控制数码管显示设计</t>
+    <t>51单片机模拟风扇控制数码管显示设计 1</t>
   </si>
   <si>
     <t>直流电机驱动模块、数码管显示模块</t>
@@ -2007,7 +2007,7 @@
     <t>P30</t>
   </si>
   <si>
-    <t>51单片机电子钟闹钟带温度LCD显示设计</t>
+    <t>51单片机电子钟闹钟带温度LCD显示设计 1</t>
   </si>
   <si>
     <t>P31</t>
@@ -2100,7 +2100,7 @@
     <t>S001</t>
   </si>
   <si>
-    <t>基于STM32语音识别蓝牙音响音箱</t>
+    <t>基于STM32语音识别蓝牙音响音箱 1</t>
   </si>
   <si>
     <t>语音识别模块、蓝牙模块、音频播放模块、音频功放模块</t>
@@ -2112,7 +2112,7 @@
     <t>S002</t>
   </si>
   <si>
-    <t>基于STM32物联网WiFi云平台温湿度烟雾报警器</t>
+    <t>基于STM32物联网WiFi云平台温湿度烟雾报警器 1</t>
   </si>
   <si>
     <t>温湿度检测、环境监测、安防报警、物联网</t>
@@ -2127,7 +2127,7 @@
     <t>S003</t>
   </si>
   <si>
-    <t>基于STM32温湿度烟雾火焰安防物联网WiFi云平台</t>
+    <t>基于STM32温湿度烟雾火焰安防物联网WiFi云平台 1</t>
   </si>
   <si>
     <t>ESP8266 WiFi模块、DHT11温湿度传感器、烟雾传感器、火焰传感器</t>
@@ -2136,7 +2136,7 @@
     <t>S004</t>
   </si>
   <si>
-    <t>基于STM32大棚温湿度土壤湿度自动灌溉WIFI远程</t>
+    <t>基于STM32大棚温湿度土壤湿度自动灌溉WIFI远程 1</t>
   </si>
   <si>
     <t>温湿度检测、农业控制、物联网</t>
@@ -2148,31 +2148,31 @@
     <t>S005</t>
   </si>
   <si>
-    <t>STM32单片机16*16点阵屏广告牌滚动显示仿真</t>
+    <t>STM32单片机16*16点阵屏广告牌滚动显示仿真 1</t>
   </si>
   <si>
     <t>S006</t>
   </si>
   <si>
-    <t>STM32病床呼叫系统LCD显示仿真</t>
+    <t>STM32病床呼叫系统LCD显示仿真 1</t>
   </si>
   <si>
     <t>S007</t>
   </si>
   <si>
-    <t>STM32电子秤LCD显示仿真</t>
+    <t>STM32电子秤LCD显示仿真 1</t>
   </si>
   <si>
     <t>S008</t>
   </si>
   <si>
-    <t>STM32简易信号发生器DDS可调幅度频率</t>
+    <t>STM32简易信号发生器DDS可调幅度频率 1</t>
   </si>
   <si>
     <t>S009</t>
   </si>
   <si>
-    <t>STM32数字秒表OLED显示</t>
+    <t>STM32数字秒表OLED显示 1</t>
   </si>
   <si>
     <t>OLED显示模块、按键模块</t>
@@ -2181,7 +2181,7 @@
     <t>S010</t>
   </si>
   <si>
-    <t>STM32远程温湿度采集监测报警OLED显示</t>
+    <t>STM32远程温湿度采集监测报警OLED显示 1</t>
   </si>
   <si>
     <t>温湿度检测、安防报警、显示与交互、物联网</t>
@@ -2193,7 +2193,7 @@
     <t>S011</t>
   </si>
   <si>
-    <t>STM32单片机光照检测智能调光系统</t>
+    <t>STM32单片机光照检测智能调光系统 1</t>
   </si>
   <si>
     <t>光敏传感器、数码管显示模块</t>
@@ -2202,7 +2202,7 @@
     <t>S012</t>
   </si>
   <si>
-    <t>STM32物联网WiFi火灾烟雾安防自动灭火报警器</t>
+    <t>STM32物联网WiFi火灾烟雾安防自动灭火报警器 1</t>
   </si>
   <si>
     <t>环境监测、安防报警、物联网</t>
@@ -2214,7 +2214,7 @@
     <t>S013</t>
   </si>
   <si>
-    <t>STM32远程WIFI温湿度烟雾监测报警OLED显示</t>
+    <t>STM32远程WIFI温湿度烟雾监测报警OLED显示 1</t>
   </si>
   <si>
     <t>温湿度检测、环境监测、安防报警、显示与交互、物联网</t>
@@ -2226,7 +2226,7 @@
     <t>S014</t>
   </si>
   <si>
-    <t>STM32温室大棚环境监测与智能调控系统</t>
+    <t>STM32温室大棚环境监测与智能调控系统 1</t>
   </si>
   <si>
     <t>环境监测、农业控制</t>
@@ -2238,7 +2238,7 @@
     <t>S015</t>
   </si>
   <si>
-    <t>基于STM32的温湿度防盗安防报警器</t>
+    <t>基于STM32的温湿度防盗安防报警器 1</t>
   </si>
   <si>
     <t>DHT11温湿度传感器、蜂鸣器</t>
@@ -2247,13 +2247,13 @@
     <t>S016</t>
   </si>
   <si>
-    <t>基于STM32的简易数字电流表</t>
+    <t>基于STM32的简易数字电流表 1</t>
   </si>
   <si>
     <t>S017</t>
   </si>
   <si>
-    <t>基于STM32的可燃气体测量报警仿真设计</t>
+    <t>基于STM32的可燃气体测量报警仿真设计 1</t>
   </si>
   <si>
     <t>环境监测、安防报警、测量仪器</t>
@@ -2262,13 +2262,13 @@
     <t>S018</t>
   </si>
   <si>
-    <t>基于STM32的简易晾衣架控制仿真设计</t>
+    <t>基于STM32的简易晾衣架控制仿真设计 1</t>
   </si>
   <si>
     <t>S019</t>
   </si>
   <si>
-    <t>基于STM32的多参数水温水质检测报警仿真设计</t>
+    <t>基于STM32的多参数水温水质检测报警仿真设计 1</t>
   </si>
   <si>
     <t>pH传感器、浊度传感器、防水温度传感器、数码管显示模块、蜂鸣器</t>
@@ -2277,7 +2277,7 @@
     <t>S020</t>
   </si>
   <si>
-    <t>基于STM32火灾烟雾浓度测量报警设计OLED显示</t>
+    <t>基于STM32火灾烟雾浓度测量报警设计OLED显示 1</t>
   </si>
   <si>
     <t>环境监测、安防报警、显示与交互、测量仪器</t>
@@ -2289,7 +2289,7 @@
     <t>S021</t>
   </si>
   <si>
-    <t>基于STM32酒精浓度测量酒驾检测报警OLED显示</t>
+    <t>基于STM32酒精浓度测量酒驾检测报警OLED显示 1</t>
   </si>
   <si>
     <t>安防报警、显示与交互、测量仪器</t>
@@ -2301,7 +2301,7 @@
     <t>S022</t>
   </si>
   <si>
-    <t>基于STM32超声波倒车雷达测距报警_OLED显示</t>
+    <t>基于STM32超声波倒车雷达测距报警_OLED显示 1</t>
   </si>
   <si>
     <t>超声波测距、安防报警、显示与交互</t>
@@ -2313,7 +2313,7 @@
     <t>S023</t>
   </si>
   <si>
-    <t>基于STM32的电子钟万年历闹钟设计_OLED显示</t>
+    <t>基于STM32的电子钟万年历闹钟设计_OLED显示 1</t>
   </si>
   <si>
     <t>OLED显示模块、RTC时钟模块</t>
@@ -2322,13 +2322,13 @@
     <t>S024</t>
   </si>
   <si>
-    <t>基于STM32的温湿度测量报警系统仿真设计</t>
+    <t>基于STM32的温湿度测量报警系统仿真设计 1</t>
   </si>
   <si>
     <t>S025</t>
   </si>
   <si>
-    <t>基于STM32的简易计算器设计_OLED显示</t>
+    <t>基于STM32的简易计算器设计_OLED显示 1</t>
   </si>
   <si>
     <t>OLED显示模块、4×4矩阵键盘、数码管显示模块</t>
@@ -2337,25 +2337,25 @@
     <t>S026</t>
   </si>
   <si>
-    <t>基于STM32的简易计算器设计_LCD1602显示</t>
+    <t>基于STM32的简易计算器设计_LCD1602显示 1</t>
   </si>
   <si>
     <t>S027</t>
   </si>
   <si>
-    <t>基于STM32的电子琴音乐播放器控制系统仿真设计</t>
+    <t>基于STM32的电子琴音乐播放器控制系统仿真设计 1</t>
   </si>
   <si>
     <t>S028</t>
   </si>
   <si>
-    <t>基于STM32的DHT11温湿度控制LCD1602显示仿真</t>
+    <t>基于STM32的DHT11温湿度控制LCD1602显示仿真 1</t>
   </si>
   <si>
     <t>S029</t>
   </si>
   <si>
-    <t>基于STM32的DHT11温湿度远程监测LCD1602显示</t>
+    <t>基于STM32的DHT11温湿度远程监测LCD1602显示 1</t>
   </si>
   <si>
     <t>温湿度检测、显示与交互、物联网</t>
@@ -2367,7 +2367,7 @@
     <t>S030</t>
   </si>
   <si>
-    <t>基于STM32的DS18B20温度远程监测LCD1602显示</t>
+    <t>基于STM32的DS18B20温度远程监测LCD1602显示 1</t>
   </si>
   <si>
     <t>ESP8266 WiFi模块、DS18B20温度传感器、LCD1602显示模块</t>
@@ -2376,25 +2376,25 @@
     <t>S031</t>
   </si>
   <si>
-    <t>基于STM32的6路抢答器Proteus仿真设计</t>
+    <t>基于STM32的6路抢答器Proteus仿真设计 1</t>
   </si>
   <si>
     <t>S032</t>
   </si>
   <si>
-    <t>基于STM32的电容电阻测量Proteus仿真设计</t>
+    <t>基于STM32的电容电阻测量Proteus仿真设计 1</t>
   </si>
   <si>
     <t>S033</t>
   </si>
   <si>
-    <t>基于STM32的电阻测量_NE555振荡电路仿真设计</t>
+    <t>基于STM32的电阻测量_NE555振荡电路仿真设计 1</t>
   </si>
   <si>
     <t>S034</t>
   </si>
   <si>
-    <t>基于STM32智能台灯仿真_自动亮度久坐提醒</t>
+    <t>基于STM32智能台灯仿真_自动亮度久坐提醒 1</t>
   </si>
   <si>
     <t>光敏传感器、LED灯模块、PWM调光模块</t>
@@ -2403,7 +2403,7 @@
     <t>S035</t>
   </si>
   <si>
-    <t>基于STM32光照测量报警仿真设计</t>
+    <t>基于STM32光照测量报警仿真设计 1</t>
   </si>
   <si>
     <t>光敏传感器、数码管显示模块、蜂鸣器</t>
@@ -2412,7 +2412,7 @@
     <t>S036</t>
   </si>
   <si>
-    <t>基于STM32的居家环境(温湿度火灾烟雾可燃气体)监测仿真设计LCD1602显示</t>
+    <t>基于STM32的居家环境(温湿度火灾烟雾可燃气体)监测仿真设计LCD1602显示 1</t>
   </si>
   <si>
     <t>温湿度检测、环境监测、显示与交互</t>
@@ -2433,7 +2433,7 @@
     <t>S038</t>
   </si>
   <si>
-    <t>基于STM32的简易温控系统LCD1602显示仿真</t>
+    <t>基于STM32的简易温控系统LCD1602显示仿真 1</t>
   </si>
   <si>
     <t>温度传感器、继电器模块、LCD1602显示模块</t>
@@ -2442,7 +2442,7 @@
     <t>S039</t>
   </si>
   <si>
-    <t>基于STM32智能灯光控制系统设计</t>
+    <t>基于STM32智能灯光控制系统设计 1</t>
   </si>
   <si>
     <t>S040</t>
@@ -2472,7 +2472,7 @@
     <t>S044</t>
   </si>
   <si>
-    <t>基于STM32篮球计分器数码管显示</t>
+    <t>基于STM32篮球计分器数码管显示 1</t>
   </si>
   <si>
     <t>S045</t>
@@ -2511,7 +2511,7 @@
     <t>S050</t>
   </si>
   <si>
-    <t>基于STM32温度报警器LCD1602显示仿真_可调温</t>
+    <t>基于STM32温度报警器LCD1602显示仿真_可调温 1</t>
   </si>
   <si>
     <t>温度传感器、LCD1602显示模块、按键模块、蜂鸣器</t>
@@ -2634,7 +2634,7 @@
     <t>S067</t>
   </si>
   <si>
-    <t>基于STM32的简易数字频率计仿真设计</t>
+    <t>基于STM32的简易数字频率计仿真设计 1</t>
   </si>
   <si>
     <t>频率测量模块、数码管显示模块</t>
@@ -2649,7 +2649,7 @@
     <t>S069</t>
   </si>
   <si>
-    <t>基于STM32的水质浑浊度和PH值监测系统设计</t>
+    <t>基于STM32的水质浑浊度和PH值监测系统设计 1</t>
   </si>
   <si>
     <t>pH传感器、浊度传感器、数码管显示模块</t>
@@ -2658,7 +2658,7 @@
     <t>S070</t>
   </si>
   <si>
-    <t>基于STM32的DHT11温湿度控制系统仿真设计</t>
+    <t>基于STM32的DHT11温湿度控制系统仿真设计 1</t>
   </si>
   <si>
     <t>DHT11温湿度传感器、继电器模块</t>
@@ -2697,13 +2697,13 @@
     <t>S075</t>
   </si>
   <si>
-    <t>基于STM32单片机RLC检测仪设计</t>
+    <t>基于STM32单片机RLC检测仪设计 1</t>
   </si>
   <si>
     <t>S076</t>
   </si>
   <si>
-    <t>基于STM32电子秤电路</t>
+    <t>基于STM32电子秤电路 1</t>
   </si>
   <si>
     <t>S077</t>
@@ -2718,7 +2718,7 @@
     <t>S078</t>
   </si>
   <si>
-    <t>基于STM32水位检测</t>
+    <t>基于STM32水位检测 1</t>
   </si>
   <si>
     <t>水位传感器、数码管显示模块</t>
@@ -2784,7 +2784,7 @@
     <t>S086</t>
   </si>
   <si>
-    <t>基于STM32智能窗帘控制仿真</t>
+    <t>基于STM32智能窗帘控制仿真 1</t>
   </si>
   <si>
     <t>S087</t>
@@ -2928,7 +2928,7 @@
     <t>S109</t>
   </si>
   <si>
-    <t>基于STM32物联网WiFi智能家居控制系统</t>
+    <t>基于STM32物联网WiFi智能家居控制系统 1</t>
   </si>
   <si>
     <t>智能家居、物联网</t>
@@ -2940,7 +2940,7 @@
     <t>S110</t>
   </si>
   <si>
-    <t>基于STM32模拟电磁炮设计</t>
+    <t>基于STM32模拟电磁炮设计 1</t>
   </si>
   <si>
     <t>升压模块、电容储能模块、MOSFET驱动模块</t>
@@ -2949,7 +2949,7 @@
     <t>S111</t>
   </si>
   <si>
-    <t>基于STM32单片机Labview空气质量监测</t>
+    <t>基于STM32单片机Labview空气质量监测 1</t>
   </si>
   <si>
     <t>空气质量传感器、串口通信模块</t>
@@ -2958,7 +2958,7 @@
     <t>S112</t>
   </si>
   <si>
-    <t>基于STM32物联网智能鱼缸智能家居系统</t>
+    <t>基于STM32物联网智能鱼缸智能家居系统 1</t>
   </si>
   <si>
     <t>ESP8266 WiFi模块、水位传感器、继电器模块、水泵模块</t>
@@ -2967,7 +2967,7 @@
     <t>S113</t>
   </si>
   <si>
-    <t>基于STM32老人防跌倒报警GSM短信GPS定位设计</t>
+    <t>基于STM32老人防跌倒报警GSM短信GPS定位设计 1</t>
   </si>
   <si>
     <t>GPS定位模块、GSM通信模块、蜂鸣器</t>
@@ -2979,13 +2979,13 @@
     <t>S114</t>
   </si>
   <si>
-    <t>51单片机的交流电流检测系统设计</t>
+    <t>51单片机的交流电流检测系统设计 1</t>
   </si>
   <si>
     <t>S115</t>
   </si>
   <si>
-    <t>基于STM32紫外线强度检测仪器蜂鸣器报警</t>
+    <t>基于STM32紫外线强度检测仪器蜂鸣器报警 1</t>
   </si>
   <si>
     <t>紫外线传感器、数码管显示模块、蜂鸣器</t>
@@ -2994,7 +2994,7 @@
     <t>S116</t>
   </si>
   <si>
-    <t>基于STM32智能充电桩计费系统的设计</t>
+    <t>基于STM32智能充电桩计费系统的设计 1</t>
   </si>
   <si>
     <t>RFID读卡模块、电能计量模块、继电器模块、LCD1602显示模块</t>
@@ -3003,7 +3003,7 @@
     <t>S117</t>
   </si>
   <si>
-    <t>基于STM32智能跟随小车_红外遥控</t>
+    <t>基于STM32智能跟随小车_红外遥控 1</t>
   </si>
   <si>
     <t>红外循迹传感器、红外遥控接收模块、电机驱动模块</t>
@@ -3012,7 +3012,7 @@
     <t>S118</t>
   </si>
   <si>
-    <t>基于STM32与ATT7022E多功能电力监测仪电路方案</t>
+    <t>基于STM32与ATT7022E多功能电力监测仪电路方案 1</t>
   </si>
   <si>
     <t>ATT7022E电能计量模块、电流互感器模块、LCD1602显示模块</t>
@@ -3021,43 +3021,43 @@
     <t>S119</t>
   </si>
   <si>
-    <t>三电极体系 弱电流检测</t>
+    <t>基于STM32三电极体系_弱电流检测 1</t>
+  </si>
+  <si>
+    <t>微弱电流检测模块、跨阻放大模块、ADC采样模块</t>
+  </si>
+  <si>
+    <t>S120</t>
+  </si>
+  <si>
+    <t>STM32三相SPWM逆变电源设计 1</t>
+  </si>
+  <si>
+    <t>三相逆变驱动模块、功率MOSFET模块、电压电流采样模块</t>
+  </si>
+  <si>
+    <t>S121</t>
+  </si>
+  <si>
+    <t>基于STM32的六路抢答器仿真</t>
+  </si>
+  <si>
+    <t>S122</t>
+  </si>
+  <si>
+    <t>基于STM32的八位抢答器仿真</t>
+  </si>
+  <si>
+    <t>X系列</t>
+  </si>
+  <si>
+    <t>X00</t>
+  </si>
+  <si>
+    <t>大功率直流电机驱动模块设计方案  0</t>
   </si>
   <si>
     <t>综合与其他</t>
-  </si>
-  <si>
-    <t>微弱电流检测模块、跨阻放大模块、ADC采样模块</t>
-  </si>
-  <si>
-    <t>S120</t>
-  </si>
-  <si>
-    <t>STM32三相SPWM逆变电源设计</t>
-  </si>
-  <si>
-    <t>三相逆变驱动模块、功率MOSFET模块、电压电流采样模块</t>
-  </si>
-  <si>
-    <t>S121</t>
-  </si>
-  <si>
-    <t>基于STM32的六路抢答器仿真</t>
-  </si>
-  <si>
-    <t>S122</t>
-  </si>
-  <si>
-    <t>基于STM32的八位抢答器仿真</t>
-  </si>
-  <si>
-    <t>X系列</t>
-  </si>
-  <si>
-    <t>X00</t>
-  </si>
-  <si>
-    <t>大功率直流电机驱动模块设计方案  0</t>
   </si>
   <si>
     <t>大功率电机驱动模块、功率MOSFET模块、PWM控制模块</t>
@@ -4578,7 +4578,7 @@
         <v>400</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T3" s="13">
         <v>2</v>
@@ -4637,7 +4637,7 @@
         <v>400</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T4" s="13">
         <v>3</v>
@@ -4652,20 +4652,20 @@
         <v>20</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -4711,20 +4711,20 @@
         <v>20</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
@@ -4770,10 +4770,10 @@
         <v>20</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>23</v>
@@ -4783,7 +4783,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -4829,20 +4829,20 @@
         <v>20</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
@@ -4888,10 +4888,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>23</v>
@@ -4901,7 +4901,7 @@
         <v>24</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
@@ -4947,20 +4947,20 @@
         <v>20</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
@@ -4991,7 +4991,7 @@
         <v>400</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T10" s="13">
         <v>9</v>
@@ -5006,20 +5006,20 @@
         <v>20</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
@@ -5065,20 +5065,20 @@
         <v>20</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
@@ -5124,20 +5124,20 @@
         <v>20</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -5183,20 +5183,20 @@
         <v>20</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
@@ -5242,20 +5242,20 @@
         <v>20</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
@@ -5298,13 +5298,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>23</v>
@@ -5314,7 +5314,7 @@
         <v>24</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="10"/>
@@ -5357,23 +5357,23 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
@@ -5416,23 +5416,23 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
@@ -5475,13 +5475,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>23</v>
@@ -5491,7 +5491,7 @@
         <v>24</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
@@ -5534,13 +5534,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>23</v>
@@ -5550,7 +5550,7 @@
         <v>24</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
@@ -5593,13 +5593,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>23</v>
@@ -5609,7 +5609,7 @@
         <v>24</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
@@ -5652,23 +5652,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
@@ -5711,13 +5711,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>23</v>
@@ -5727,12 +5727,12 @@
         <v>24</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L23" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H23="",0,LEN(H23)-LEN(SUBSTITUTE(H23,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H23)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H23)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H23)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H23)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H23)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H23)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H23)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H23)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H23)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H23)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H23)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H23)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H23)),1,0)))</f>
@@ -5772,23 +5772,23 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
@@ -5831,13 +5831,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>23</v>
@@ -5847,7 +5847,7 @@
         <v>24</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
@@ -5890,13 +5890,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>23</v>
@@ -5906,7 +5906,7 @@
         <v>24</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
@@ -5949,13 +5949,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>23</v>
@@ -5965,7 +5965,7 @@
         <v>24</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
@@ -6008,23 +6008,23 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
@@ -6067,28 +6067,28 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L29" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H29="",0,LEN(H29)-LEN(SUBSTITUTE(H29,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H29)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H29)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H29)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H29)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H29)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H29)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H29)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H29)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H29)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H29)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H29)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H29)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H29)),1,0)))</f>
@@ -6128,23 +6128,23 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F30" s="11"/>
       <c r="G30" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
@@ -6187,28 +6187,28 @@
         <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
       <c r="K31" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L31" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H31="",0,LEN(H31)-LEN(SUBSTITUTE(H31,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H31)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H31)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H31)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H31)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H31)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H31)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H31)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H31)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H31)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H31)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H31)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H31)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H31)),1,0)))</f>
@@ -6248,23 +6248,23 @@
         <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="10"/>
@@ -6307,23 +6307,23 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
@@ -6366,23 +6366,23 @@
         <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
@@ -6425,23 +6425,23 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
@@ -6484,23 +6484,23 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
@@ -6531,7 +6531,7 @@
         <v>400</v>
       </c>
       <c r="S36" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T36" s="13">
         <v>35</v>
@@ -6543,13 +6543,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>23</v>
@@ -6559,7 +6559,7 @@
         <v>24</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="10"/>
@@ -6590,7 +6590,7 @@
         <v>400</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T37" s="13">
         <v>36</v>
@@ -6602,23 +6602,23 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
@@ -6649,7 +6649,7 @@
         <v>400</v>
       </c>
       <c r="S38" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T38" s="13">
         <v>37</v>
@@ -6661,23 +6661,23 @@
         <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
@@ -6708,7 +6708,7 @@
         <v>400</v>
       </c>
       <c r="S39" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T39" s="13">
         <v>38</v>
@@ -6720,23 +6720,23 @@
         <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="11"/>
       <c r="G40" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="10"/>
@@ -6767,7 +6767,7 @@
         <v>400</v>
       </c>
       <c r="S40" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T40" s="13">
         <v>39</v>
@@ -6779,23 +6779,23 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F41" s="11"/>
       <c r="G41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="10"/>
@@ -6826,7 +6826,7 @@
         <v>400</v>
       </c>
       <c r="S41" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T41" s="13">
         <v>40</v>
@@ -6838,23 +6838,23 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F42" s="11"/>
       <c r="G42" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
@@ -6885,7 +6885,7 @@
         <v>400</v>
       </c>
       <c r="S42" s="8" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="T42" s="13">
         <v>41</v>
@@ -6897,7 +6897,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>168</v>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="F43" s="11"/>
       <c r="G43" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>170</v>
@@ -6944,7 +6944,7 @@
         <v>400</v>
       </c>
       <c r="S43" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T43" s="13">
         <v>42</v>
@@ -6956,7 +6956,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>171</v>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="F44" s="11"/>
       <c r="G44" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>173</v>
@@ -7003,7 +7003,7 @@
         <v>400</v>
       </c>
       <c r="S44" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T44" s="13">
         <v>43</v>
@@ -7015,7 +7015,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>174</v>
@@ -7062,7 +7062,7 @@
         <v>400</v>
       </c>
       <c r="S45" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T45" s="13">
         <v>44</v>
@@ -7074,7 +7074,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>177</v>
@@ -7121,7 +7121,7 @@
         <v>400</v>
       </c>
       <c r="S46" s="8" t="s">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="T46" s="13">
         <v>45</v>
@@ -7133,7 +7133,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>180</v>
@@ -7180,7 +7180,7 @@
         <v>400</v>
       </c>
       <c r="S47" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T47" s="13">
         <v>46</v>
@@ -7192,7 +7192,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>183</v>
@@ -7239,7 +7239,7 @@
         <v>400</v>
       </c>
       <c r="S48" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T48" s="13">
         <v>47</v>
@@ -7251,7 +7251,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>187</v>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="F49" s="11"/>
       <c r="G49" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>189</v>
@@ -7298,7 +7298,7 @@
         <v>400</v>
       </c>
       <c r="S49" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T49" s="13">
         <v>48</v>
@@ -7310,7 +7310,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>190</v>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="F50" s="11"/>
       <c r="G50" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>192</v>
@@ -7357,7 +7357,7 @@
         <v>400</v>
       </c>
       <c r="S50" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T50" s="13">
         <v>49</v>
@@ -7369,7 +7369,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>193</v>
@@ -7416,7 +7416,7 @@
         <v>400</v>
       </c>
       <c r="S51" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T51" s="13">
         <v>50</v>
@@ -7428,7 +7428,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>196</v>
@@ -7487,7 +7487,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>199</v>
@@ -7503,7 +7503,7 @@
         <v>24</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I53" s="10"/>
       <c r="J53" s="10"/>
@@ -7546,7 +7546,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>201</v>
@@ -7562,7 +7562,7 @@
         <v>24</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I54" s="10"/>
       <c r="J54" s="10"/>
@@ -7605,7 +7605,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>203</v>
@@ -7652,7 +7652,7 @@
         <v>400</v>
       </c>
       <c r="S55" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T55" s="13">
         <v>54</v>
@@ -7664,7 +7664,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>205</v>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="F56" s="11"/>
       <c r="G56" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>207</v>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="F57" s="11"/>
       <c r="G57" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>211</v>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="F58" s="11"/>
       <c r="G58" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>214</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F59" s="11"/>
       <c r="G59" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>217</v>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="F61" s="11"/>
       <c r="G61" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>222</v>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="F62" s="11"/>
       <c r="G62" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>222</v>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="F63" s="11"/>
       <c r="G63" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>214</v>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="F64" s="11"/>
       <c r="G64" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>214</v>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F65" s="11"/>
       <c r="G65" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>231</v>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="F66" s="11"/>
       <c r="G66" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H66" s="10" t="s">
         <v>234</v>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="F67" s="11"/>
       <c r="G67" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>211</v>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="F69" s="11"/>
       <c r="G69" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>214</v>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="F70" s="11"/>
       <c r="G70" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H70" s="10" t="s">
         <v>244</v>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="F71" s="11"/>
       <c r="G71" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>214</v>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="F72" s="11"/>
       <c r="G72" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>217</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F73" s="11"/>
       <c r="G73" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>211</v>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="F74" s="11"/>
       <c r="G74" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>211</v>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F75" s="11"/>
       <c r="G75" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>214</v>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="F76" s="11"/>
       <c r="G76" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>257</v>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F77" s="11"/>
       <c r="G77" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>207</v>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="F78" s="11"/>
       <c r="G78" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H78" s="10" t="s">
         <v>262</v>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F79" s="11"/>
       <c r="G79" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>265</v>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="F80" s="11"/>
       <c r="G80" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>265</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="F81" s="11"/>
       <c r="G81" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>214</v>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="F82" s="11"/>
       <c r="G82" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H82" s="10" t="s">
         <v>214</v>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="F83" s="11"/>
       <c r="G83" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>214</v>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F84" s="11"/>
       <c r="G84" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>214</v>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="F85" s="11"/>
       <c r="G85" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>217</v>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="F86" s="11"/>
       <c r="G86" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H86" s="10" t="s">
         <v>280</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="F87" s="11"/>
       <c r="G87" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H87" s="10" t="s">
         <v>211</v>
@@ -9540,7 +9540,7 @@
         <v>400</v>
       </c>
       <c r="S87" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T87" s="13">
         <v>86</v>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="F88" s="11"/>
       <c r="G88" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>214</v>
@@ -9626,7 +9626,7 @@
         <v>288</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H89" s="10" t="s">
         <v>217</v>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F90" s="11"/>
       <c r="G90" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>198</v>
@@ -9929,7 +9929,7 @@
       <c r="I94" s="10"/>
       <c r="J94" s="10"/>
       <c r="K94" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L94" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H94="",0,LEN(H94)-LEN(SUBSTITUTE(H94,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H94)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H94)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H94)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H94)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H94)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H94)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H94)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H94)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H94)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H94)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H94)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H94)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H94)),1,0)))</f>
@@ -9957,7 +9957,7 @@
         <v>400</v>
       </c>
       <c r="S94" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T94" s="13">
         <v>93</v>
@@ -9985,7 +9985,7 @@
         <v>305</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I95" s="10"/>
       <c r="J95" s="10"/>
@@ -10100,15 +10100,15 @@
       </c>
       <c r="F97" s="11"/>
       <c r="G97" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I97" s="10"/>
       <c r="J97" s="10"/>
       <c r="K97" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L97" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H97="",0,LEN(H97)-LEN(SUBSTITUTE(H97,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H97)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H97)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H97)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H97)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H97)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H97)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H97)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H97)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H97)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H97)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H97)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H97)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H97)),1,0)))</f>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F101" s="11"/>
       <c r="G101" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>323</v>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="F102" s="11"/>
       <c r="G102" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>326</v>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="F103" s="11"/>
       <c r="G103" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>329</v>
@@ -10574,7 +10574,7 @@
       </c>
       <c r="F105" s="11"/>
       <c r="G105" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>336</v>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="F108" s="11"/>
       <c r="G108" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>179</v>
@@ -10813,7 +10813,7 @@
         <v>345</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="F110" s="11"/>
       <c r="G110" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>348</v>
@@ -11316,7 +11316,7 @@
         <v>400</v>
       </c>
       <c r="S117" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T117" s="13">
         <v>116</v>
@@ -11344,7 +11344,7 @@
         <v>24</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I118" s="10"/>
       <c r="J118" s="10"/>
@@ -11459,10 +11459,10 @@
       </c>
       <c r="F120" s="11"/>
       <c r="G120" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H120" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I120" s="10"/>
       <c r="J120" s="10"/>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="F122" s="11"/>
       <c r="G122" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H122" s="10" t="s">
         <v>383</v>
@@ -11639,7 +11639,7 @@
         <v>24</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I123" s="10"/>
       <c r="J123" s="10"/>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="F124" s="11"/>
       <c r="G124" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H124" s="10" t="s">
         <v>388</v>
@@ -11754,10 +11754,10 @@
       </c>
       <c r="F125" s="11"/>
       <c r="G125" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I125" s="10"/>
       <c r="J125" s="10"/>
@@ -11847,7 +11847,7 @@
         <v>400</v>
       </c>
       <c r="S126" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T126" s="13">
         <v>125</v>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="F127" s="11"/>
       <c r="G127" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>396</v>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="F128" s="11"/>
       <c r="G128" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>396</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="F129" s="11"/>
       <c r="G129" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>396</v>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="F130" s="11"/>
       <c r="G130" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H130" s="10" t="s">
         <v>396</v>
@@ -12108,7 +12108,7 @@
       </c>
       <c r="F131" s="11"/>
       <c r="G131" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>405</v>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="F132" s="11"/>
       <c r="G132" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H132" s="10" t="s">
         <v>408</v>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="F133" s="11"/>
       <c r="G133" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H133" s="10" t="s">
         <v>411</v>
@@ -12406,7 +12406,7 @@
         <v>24</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I136" s="10"/>
       <c r="J136" s="10"/>
@@ -12465,7 +12465,7 @@
         <v>24</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I137" s="10"/>
       <c r="J137" s="10"/>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F138" s="11"/>
       <c r="G138" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>198</v>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F139" s="11"/>
       <c r="G139" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>427</v>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="F140" s="11"/>
       <c r="G140" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>430</v>
@@ -12819,7 +12819,7 @@
         <v>24</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I143" s="10"/>
       <c r="J143" s="10"/>
@@ -12934,7 +12934,7 @@
       </c>
       <c r="F145" s="11"/>
       <c r="G145" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>444</v>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="F148" s="11"/>
       <c r="G148" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>452</v>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="F149" s="11"/>
       <c r="G149" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>455</v>
@@ -13465,7 +13465,7 @@
       </c>
       <c r="F154" s="11"/>
       <c r="G154" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H154" s="10" t="s">
         <v>471</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="F157" s="11"/>
       <c r="G157" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>481</v>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="F159" s="11"/>
       <c r="G159" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H159" s="10" t="s">
         <v>488</v>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="F160" s="11"/>
       <c r="G160" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H160" s="10" t="s">
         <v>491</v>
@@ -14530,7 +14530,7 @@
         <v>24</v>
       </c>
       <c r="H172" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I172" s="10"/>
       <c r="J172" s="10"/>
@@ -14645,7 +14645,7 @@
       </c>
       <c r="F174" s="11"/>
       <c r="G174" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H174" s="10" t="s">
         <v>527</v>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="F177" s="11"/>
       <c r="G177" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H177" s="10" t="s">
         <v>537</v>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="F179" s="11"/>
       <c r="G179" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H179" s="10" t="s">
         <v>543</v>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="F180" s="11"/>
       <c r="G180" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H180" s="10" t="s">
         <v>198</v>
@@ -15120,7 +15120,7 @@
         <v>24</v>
       </c>
       <c r="H182" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I182" s="10"/>
       <c r="J182" s="10"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="F184" s="11"/>
       <c r="G184" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H184" s="10" t="s">
         <v>554</v>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="F188" s="11"/>
       <c r="G188" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H188" s="10" t="s">
         <v>566</v>
@@ -15648,10 +15648,10 @@
       </c>
       <c r="F191" s="11"/>
       <c r="G191" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H191" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I191" s="10"/>
       <c r="J191" s="10"/>
@@ -15710,7 +15710,7 @@
         <v>24</v>
       </c>
       <c r="H192" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
@@ -15827,7 +15827,7 @@
         <v>288</v>
       </c>
       <c r="G194" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H194" s="10" t="s">
         <v>217</v>
@@ -16063,10 +16063,10 @@
       </c>
       <c r="F198" s="11"/>
       <c r="G198" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H198" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I198" s="10"/>
       <c r="J198" s="10"/>
@@ -16181,7 +16181,7 @@
       </c>
       <c r="F200" s="11"/>
       <c r="G200" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H200" s="10" t="s">
         <v>600</v>
@@ -16215,7 +16215,7 @@
         <v>400</v>
       </c>
       <c r="S200" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T200" s="13">
         <v>199</v>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="F201" s="11"/>
       <c r="G201" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H201" s="10" t="s">
         <v>603</v>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="F204" s="11"/>
       <c r="G204" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H204" s="10" t="s">
         <v>452</v>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="F205" s="11"/>
       <c r="G205" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H205" s="10" t="s">
         <v>612</v>
@@ -16535,7 +16535,7 @@
       </c>
       <c r="F206" s="11"/>
       <c r="G206" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H206" s="10" t="s">
         <v>615</v>
@@ -16594,7 +16594,7 @@
       </c>
       <c r="F207" s="11"/>
       <c r="G207" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H207" s="10" t="s">
         <v>198</v>
@@ -16656,7 +16656,7 @@
         <v>24</v>
       </c>
       <c r="H208" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I208" s="10"/>
       <c r="J208" s="10"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F209" s="11"/>
       <c r="G209" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H209" s="10" t="s">
         <v>170</v>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="F211" s="11"/>
       <c r="G211" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H211" s="10" t="s">
         <v>627</v>
@@ -16951,7 +16951,7 @@
         <v>24</v>
       </c>
       <c r="H213" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I213" s="10"/>
       <c r="J213" s="10"/>
@@ -17125,7 +17125,7 @@
       </c>
       <c r="F216" s="11"/>
       <c r="G216" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H216" s="10" t="s">
         <v>603</v>
@@ -17159,7 +17159,7 @@
         <v>400</v>
       </c>
       <c r="S216" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T216" s="13">
         <v>215</v>
@@ -17184,10 +17184,10 @@
       </c>
       <c r="F217" s="11"/>
       <c r="G217" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H217" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I217" s="10"/>
       <c r="J217" s="10"/>
@@ -17218,7 +17218,7 @@
         <v>400</v>
       </c>
       <c r="S217" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T217" s="13">
         <v>216</v>
@@ -17277,7 +17277,7 @@
         <v>400</v>
       </c>
       <c r="S218" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T218" s="13">
         <v>217</v>
@@ -17336,7 +17336,7 @@
         <v>400</v>
       </c>
       <c r="S219" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T219" s="13">
         <v>218</v>
@@ -17361,7 +17361,7 @@
       </c>
       <c r="F220" s="11"/>
       <c r="G220" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H220" s="10" t="s">
         <v>648</v>
@@ -17395,7 +17395,7 @@
         <v>400</v>
       </c>
       <c r="S220" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T220" s="13">
         <v>219</v>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="F221" s="11"/>
       <c r="G221" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H221" s="10" t="s">
         <v>627</v>
@@ -17454,7 +17454,7 @@
         <v>400</v>
       </c>
       <c r="S221" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T221" s="13">
         <v>220</v>
@@ -17479,10 +17479,10 @@
       </c>
       <c r="F222" s="11"/>
       <c r="G222" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H222" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I222" s="10"/>
       <c r="J222" s="10"/>
@@ -17513,7 +17513,7 @@
         <v>400</v>
       </c>
       <c r="S222" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T222" s="13">
         <v>221</v>
@@ -17538,10 +17538,10 @@
       </c>
       <c r="F223" s="11"/>
       <c r="G223" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H223" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I223" s="10"/>
       <c r="J223" s="10"/>
@@ -17572,7 +17572,7 @@
         <v>400</v>
       </c>
       <c r="S223" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T223" s="13">
         <v>222</v>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="F224" s="11"/>
       <c r="G224" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H224" s="10" t="s">
         <v>657</v>
@@ -17631,7 +17631,7 @@
         <v>400</v>
       </c>
       <c r="S224" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T224" s="13">
         <v>223</v>
@@ -17690,7 +17690,7 @@
         <v>400</v>
       </c>
       <c r="S225" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T225" s="13">
         <v>224</v>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="F238" s="11"/>
       <c r="G238" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H238" s="10" t="s">
         <v>691</v>
@@ -18465,7 +18465,7 @@
         <v>400</v>
       </c>
       <c r="S238" s="8" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="T238" s="13">
         <v>237</v>
@@ -18528,7 +18528,7 @@
         <v>400</v>
       </c>
       <c r="S239" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T239" s="13">
         <v>238</v>
@@ -18591,7 +18591,7 @@
         <v>400</v>
       </c>
       <c r="S240" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T240" s="13">
         <v>239</v>
@@ -18624,7 +18624,7 @@
       <c r="I241" s="10"/>
       <c r="J241" s="10"/>
       <c r="K241" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L241" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H241="",0,LEN(H241)-LEN(SUBSTITUTE(H241,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H241)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H241)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H241)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H241)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H241)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H241)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H241)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H241)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H241)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H241)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H241)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H241)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H241)),1,0)))</f>
@@ -18654,7 +18654,7 @@
         <v>400</v>
       </c>
       <c r="S241" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T241" s="13">
         <v>240</v>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="F242" s="11"/>
       <c r="G242" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H242" s="10" t="s">
         <v>627</v>
@@ -18715,7 +18715,7 @@
         <v>400</v>
       </c>
       <c r="S242" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T242" s="13">
         <v>241</v>
@@ -18776,7 +18776,7 @@
         <v>400</v>
       </c>
       <c r="S243" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T243" s="13">
         <v>242</v>
@@ -18837,7 +18837,7 @@
         <v>400</v>
       </c>
       <c r="S244" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T244" s="13">
         <v>243</v>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="F245" s="11"/>
       <c r="G245" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H245" s="10" t="s">
         <v>444</v>
@@ -18898,7 +18898,7 @@
         <v>400</v>
       </c>
       <c r="S245" s="8" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="T245" s="13">
         <v>244</v>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="F246" s="11"/>
       <c r="G246" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H246" s="10" t="s">
         <v>715</v>
@@ -18959,7 +18959,7 @@
         <v>400</v>
       </c>
       <c r="S246" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T246" s="13">
         <v>245</v>
@@ -18992,7 +18992,7 @@
       <c r="I247" s="10"/>
       <c r="J247" s="10"/>
       <c r="K247" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L247" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H247="",0,LEN(H247)-LEN(SUBSTITUTE(H247,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H247)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H247)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H247)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H247)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H247)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H247)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H247)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H247)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H247)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H247)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H247)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H247)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H247)),1,0)))</f>
@@ -19022,7 +19022,7 @@
         <v>400</v>
       </c>
       <c r="S247" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T247" s="13">
         <v>246</v>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="F248" s="11"/>
       <c r="G248" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H248" s="10" t="s">
         <v>722</v>
@@ -19083,7 +19083,7 @@
         <v>400</v>
       </c>
       <c r="S248" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T248" s="13">
         <v>247</v>
@@ -19116,7 +19116,7 @@
       <c r="I249" s="10"/>
       <c r="J249" s="10"/>
       <c r="K249" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L249" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H249="",0,LEN(H249)-LEN(SUBSTITUTE(H249,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H249)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H249)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H249)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H249)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H249)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H249)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H249)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H249)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H249)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H249)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H249)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H249)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H249)),1,0)))</f>
@@ -19146,7 +19146,7 @@
         <v>400</v>
       </c>
       <c r="S249" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T249" s="13">
         <v>248</v>
@@ -19179,7 +19179,7 @@
       <c r="I250" s="10"/>
       <c r="J250" s="10"/>
       <c r="K250" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L250" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H250="",0,LEN(H250)-LEN(SUBSTITUTE(H250,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H250)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H250)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H250)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H250)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H250)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H250)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H250)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H250)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H250)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H250)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H250)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H250)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H250)),1,0)))</f>
@@ -19209,7 +19209,7 @@
         <v>400</v>
       </c>
       <c r="S250" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T250" s="13">
         <v>249</v>
@@ -19270,7 +19270,7 @@
         <v>400</v>
       </c>
       <c r="S251" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T251" s="13">
         <v>250</v>
@@ -19331,7 +19331,7 @@
         <v>400</v>
       </c>
       <c r="S252" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T252" s="13">
         <v>251</v>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="F253" s="11"/>
       <c r="G253" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H253" s="10" t="s">
         <v>478</v>
@@ -19392,7 +19392,7 @@
         <v>400</v>
       </c>
       <c r="S253" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T253" s="13">
         <v>252</v>
@@ -19420,7 +19420,7 @@
         <v>742</v>
       </c>
       <c r="H254" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I254" s="10"/>
       <c r="J254" s="10"/>
@@ -19453,7 +19453,7 @@
         <v>400</v>
       </c>
       <c r="S254" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T254" s="13">
         <v>253</v>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="F255" s="11"/>
       <c r="G255" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H255" s="10" t="s">
         <v>554</v>
@@ -19514,7 +19514,7 @@
         <v>400</v>
       </c>
       <c r="S255" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T255" s="13">
         <v>254</v>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="F256" s="11"/>
       <c r="G256" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H256" s="10" t="s">
         <v>747</v>
@@ -19575,7 +19575,7 @@
         <v>400</v>
       </c>
       <c r="S256" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T256" s="13">
         <v>255</v>
@@ -19636,7 +19636,7 @@
         <v>400</v>
       </c>
       <c r="S257" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T257" s="13">
         <v>256</v>
@@ -19697,7 +19697,7 @@
         <v>400</v>
       </c>
       <c r="S258" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T258" s="13">
         <v>257</v>
@@ -19758,7 +19758,7 @@
         <v>400</v>
       </c>
       <c r="S259" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T259" s="13">
         <v>258</v>
@@ -19783,7 +19783,7 @@
       </c>
       <c r="F260" s="11"/>
       <c r="G260" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H260" s="10" t="s">
         <v>762</v>
@@ -19819,7 +19819,7 @@
         <v>400</v>
       </c>
       <c r="S260" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T260" s="13">
         <v>259</v>
@@ -19880,7 +19880,7 @@
         <v>400</v>
       </c>
       <c r="S261" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T261" s="13">
         <v>260</v>
@@ -19905,7 +19905,7 @@
       </c>
       <c r="F262" s="11"/>
       <c r="G262" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H262" s="10" t="s">
         <v>767</v>
@@ -19941,7 +19941,7 @@
         <v>400</v>
       </c>
       <c r="S262" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T262" s="13">
         <v>261</v>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="F263" s="11"/>
       <c r="G263" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H263" s="10" t="s">
         <v>600</v>
@@ -20002,7 +20002,7 @@
         <v>400</v>
       </c>
       <c r="S263" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T263" s="13">
         <v>262</v>
@@ -20027,10 +20027,10 @@
       </c>
       <c r="F264" s="11"/>
       <c r="G264" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H264" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I264" s="10"/>
       <c r="J264" s="10"/>
@@ -20063,7 +20063,7 @@
         <v>400</v>
       </c>
       <c r="S264" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T264" s="13">
         <v>263</v>
@@ -20124,7 +20124,7 @@
         <v>400</v>
       </c>
       <c r="S265" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T265" s="13">
         <v>264</v>
@@ -20157,7 +20157,7 @@
       <c r="I266" s="10"/>
       <c r="J266" s="10"/>
       <c r="K266" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L266" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H266="",0,LEN(H266)-LEN(SUBSTITUTE(H266,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H266)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H266)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H266)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H266)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H266)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H266)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H266)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H266)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H266)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H266)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H266)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H266)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H266)),1,0)))</f>
@@ -20187,7 +20187,7 @@
         <v>400</v>
       </c>
       <c r="S266" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T266" s="13">
         <v>265</v>
@@ -20220,7 +20220,7 @@
       <c r="I267" s="10"/>
       <c r="J267" s="10"/>
       <c r="K267" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L267" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H267="",0,LEN(H267)-LEN(SUBSTITUTE(H267,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H267)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H267)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H267)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H267)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H267)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H267)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H267)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H267)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H267)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H267)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H267)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H267)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H267)),1,0)))</f>
@@ -20250,7 +20250,7 @@
         <v>400</v>
       </c>
       <c r="S267" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T267" s="13">
         <v>266</v>
@@ -20311,7 +20311,7 @@
         <v>400</v>
       </c>
       <c r="S268" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T268" s="13">
         <v>267</v>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="F269" s="11"/>
       <c r="G269" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>396</v>
@@ -20372,7 +20372,7 @@
         <v>400</v>
       </c>
       <c r="S269" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T269" s="13">
         <v>268</v>
@@ -20397,7 +20397,7 @@
       </c>
       <c r="F270" s="11"/>
       <c r="G270" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H270" s="10" t="s">
         <v>396</v>
@@ -20433,7 +20433,7 @@
         <v>400</v>
       </c>
       <c r="S270" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T270" s="13">
         <v>269</v>
@@ -20458,7 +20458,7 @@
       </c>
       <c r="F271" s="11"/>
       <c r="G271" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H271" s="10" t="s">
         <v>789</v>
@@ -20494,7 +20494,7 @@
         <v>400</v>
       </c>
       <c r="S271" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T271" s="13">
         <v>270</v>
@@ -20555,7 +20555,7 @@
         <v>400</v>
       </c>
       <c r="S272" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T272" s="13">
         <v>271</v>
@@ -20616,7 +20616,7 @@
         <v>400</v>
       </c>
       <c r="S273" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T273" s="13">
         <v>272</v>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="F275" s="11"/>
       <c r="G275" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H275" s="10" t="s">
         <v>802</v>
@@ -20738,7 +20738,7 @@
         <v>400</v>
       </c>
       <c r="S275" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T275" s="13">
         <v>274</v>
@@ -20799,7 +20799,7 @@
         <v>400</v>
       </c>
       <c r="S276" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T276" s="13">
         <v>275</v>
@@ -20824,10 +20824,10 @@
       </c>
       <c r="F277" s="11"/>
       <c r="G277" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H277" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I277" s="10"/>
       <c r="J277" s="10"/>
@@ -20888,7 +20888,7 @@
         <v>24</v>
       </c>
       <c r="H278" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I278" s="10"/>
       <c r="J278" s="10"/>
@@ -20946,10 +20946,10 @@
       </c>
       <c r="F279" s="11"/>
       <c r="G279" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H279" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I279" s="10"/>
       <c r="J279" s="10"/>
@@ -21010,7 +21010,7 @@
         <v>24</v>
       </c>
       <c r="H280" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I280" s="10"/>
       <c r="J280" s="10"/>
@@ -21068,7 +21068,7 @@
       </c>
       <c r="F281" s="11"/>
       <c r="G281" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H281" s="10" t="s">
         <v>198</v>
@@ -21104,7 +21104,7 @@
         <v>400</v>
       </c>
       <c r="S281" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T281" s="13">
         <v>280</v>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="F282" s="11"/>
       <c r="G282" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H282" s="10" t="s">
         <v>198</v>
@@ -21312,7 +21312,7 @@
       </c>
       <c r="F285" s="11"/>
       <c r="G285" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H285" s="10" t="s">
         <v>320</v>
@@ -21373,7 +21373,7 @@
       </c>
       <c r="F286" s="11"/>
       <c r="G286" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H286" s="10" t="s">
         <v>825</v>
@@ -21409,7 +21409,7 @@
         <v>400</v>
       </c>
       <c r="S286" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T286" s="13">
         <v>285</v>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="F287" s="11"/>
       <c r="G287" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H287" s="10" t="s">
         <v>828</v>
@@ -21470,7 +21470,7 @@
         <v>400</v>
       </c>
       <c r="S287" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T287" s="13">
         <v>286</v>
@@ -21556,7 +21556,7 @@
       </c>
       <c r="F289" s="11"/>
       <c r="G289" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H289" s="10" t="s">
         <v>648</v>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="F290" s="11"/>
       <c r="G290" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H290" s="10" t="s">
         <v>836</v>
@@ -21739,7 +21739,7 @@
       </c>
       <c r="F292" s="11"/>
       <c r="G292" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H292" s="10" t="s">
         <v>214</v>
@@ -21800,7 +21800,7 @@
       </c>
       <c r="F293" s="11"/>
       <c r="G293" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>842</v>
@@ -21922,10 +21922,10 @@
       </c>
       <c r="F295" s="11"/>
       <c r="G295" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H295" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I295" s="10"/>
       <c r="J295" s="10"/>
@@ -22105,7 +22105,7 @@
       </c>
       <c r="F298" s="11"/>
       <c r="G298" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H298" s="10" t="s">
         <v>481</v>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F299" s="11"/>
       <c r="G299" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H299" s="10" t="s">
         <v>856</v>
@@ -22227,7 +22227,7 @@
       </c>
       <c r="F300" s="11"/>
       <c r="G300" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H300" s="10" t="s">
         <v>859</v>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="F301" s="11"/>
       <c r="G301" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H301" s="10" t="s">
         <v>862</v>
@@ -22349,10 +22349,10 @@
       </c>
       <c r="F302" s="11"/>
       <c r="G302" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H302" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I302" s="10"/>
       <c r="J302" s="10"/>
@@ -22410,10 +22410,10 @@
       </c>
       <c r="F303" s="11"/>
       <c r="G303" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H303" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I303" s="10"/>
       <c r="J303" s="10"/>
@@ -22471,7 +22471,7 @@
       </c>
       <c r="F304" s="11"/>
       <c r="G304" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H304" s="10" t="s">
         <v>869</v>
@@ -22507,7 +22507,7 @@
         <v>400</v>
       </c>
       <c r="S304" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T304" s="13">
         <v>303</v>
@@ -22629,7 +22629,7 @@
         <v>400</v>
       </c>
       <c r="S306" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T306" s="13">
         <v>305</v>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="F307" s="11"/>
       <c r="G307" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H307" s="10" t="s">
         <v>877</v>
@@ -22690,7 +22690,7 @@
         <v>400</v>
       </c>
       <c r="S307" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T307" s="13">
         <v>306</v>
@@ -22715,7 +22715,7 @@
       </c>
       <c r="F308" s="11"/>
       <c r="G308" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H308" s="10" t="s">
         <v>336</v>
@@ -22776,7 +22776,7 @@
       </c>
       <c r="F309" s="11"/>
       <c r="G309" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H309" s="10" t="s">
         <v>882</v>
@@ -22837,7 +22837,7 @@
       </c>
       <c r="F310" s="11"/>
       <c r="G310" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H310" s="10" t="s">
         <v>214</v>
@@ -22995,7 +22995,7 @@
         <v>400</v>
       </c>
       <c r="S312" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T312" s="13">
         <v>311</v>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="F313" s="11"/>
       <c r="G313" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H313" s="10" t="s">
         <v>173</v>
@@ -23056,7 +23056,7 @@
         <v>400</v>
       </c>
       <c r="S313" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T313" s="13">
         <v>312</v>
@@ -23178,7 +23178,7 @@
         <v>400</v>
       </c>
       <c r="S315" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T315" s="13">
         <v>314</v>
@@ -23203,7 +23203,7 @@
       </c>
       <c r="F316" s="11"/>
       <c r="G316" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H316" s="10" t="s">
         <v>900</v>
@@ -23264,7 +23264,7 @@
       </c>
       <c r="F317" s="11"/>
       <c r="G317" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H317" s="10" t="s">
         <v>903</v>
@@ -23447,7 +23447,7 @@
       </c>
       <c r="F320" s="11"/>
       <c r="G320" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H320" s="10" t="s">
         <v>354</v>
@@ -23630,7 +23630,7 @@
       </c>
       <c r="F323" s="11"/>
       <c r="G323" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H323" s="10" t="s">
         <v>527</v>
@@ -23666,7 +23666,7 @@
         <v>400</v>
       </c>
       <c r="S323" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T323" s="13">
         <v>322</v>
@@ -23694,7 +23694,7 @@
         <v>24</v>
       </c>
       <c r="H324" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I324" s="10"/>
       <c r="J324" s="10"/>
@@ -23754,7 +23754,7 @@
         <v>923</v>
       </c>
       <c r="G325" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H325" s="10" t="s">
         <v>543</v>
@@ -23790,7 +23790,7 @@
         <v>400</v>
       </c>
       <c r="S325" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T325" s="13">
         <v>324</v>
@@ -23815,7 +23815,7 @@
       </c>
       <c r="F326" s="11"/>
       <c r="G326" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H326" s="10" t="s">
         <v>926</v>
@@ -23853,7 +23853,7 @@
         <v>400</v>
       </c>
       <c r="S326" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T326" s="13">
         <v>325</v>
@@ -23886,7 +23886,7 @@
       <c r="I327" s="10"/>
       <c r="J327" s="10"/>
       <c r="K327" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L327" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H327="",0,LEN(H327)-LEN(SUBSTITUTE(H327,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H327)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H327)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H327)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H327)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H327)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H327)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H327)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H327)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H327)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H327)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H327)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H327)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H327)),1,0)))</f>
@@ -23916,7 +23916,7 @@
         <v>400</v>
       </c>
       <c r="S327" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T327" s="13">
         <v>326</v>
@@ -23941,7 +23941,7 @@
       </c>
       <c r="F328" s="11"/>
       <c r="G328" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H328" s="10" t="s">
         <v>934</v>
@@ -23979,7 +23979,7 @@
         <v>400</v>
       </c>
       <c r="S328" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T328" s="13">
         <v>327</v>
@@ -24004,15 +24004,15 @@
       </c>
       <c r="F329" s="11"/>
       <c r="G329" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H329" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I329" s="10"/>
       <c r="J329" s="10"/>
       <c r="K329" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L329" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H329="",0,LEN(H329)-LEN(SUBSTITUTE(H329,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H329)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H329)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H329)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H329)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H329)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H329)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H329)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H329)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H329)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H329)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H329)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H329)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H329)),1,0)))</f>
@@ -24042,7 +24042,7 @@
         <v>400</v>
       </c>
       <c r="S329" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T329" s="13">
         <v>328</v>
@@ -24067,7 +24067,7 @@
       </c>
       <c r="F330" s="11"/>
       <c r="G330" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H330" s="10" t="s">
         <v>862</v>
@@ -24103,7 +24103,7 @@
         <v>400</v>
       </c>
       <c r="S330" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T330" s="13">
         <v>329</v>
@@ -24136,7 +24136,7 @@
       <c r="I331" s="10"/>
       <c r="J331" s="10"/>
       <c r="K331" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L331" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H331="",0,LEN(H331)-LEN(SUBSTITUTE(H331,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H331)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H331)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H331)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H331)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H331)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H331)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H331)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H331)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H331)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H331)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H331)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H331)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H331)),1,0)))</f>
@@ -24166,7 +24166,7 @@
         <v>400</v>
       </c>
       <c r="S331" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T331" s="13">
         <v>330</v>
@@ -24191,15 +24191,15 @@
       </c>
       <c r="F332" s="11"/>
       <c r="G332" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H332" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I332" s="10"/>
       <c r="J332" s="10"/>
       <c r="K332" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L332" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H332="",0,LEN(H332)-LEN(SUBSTITUTE(H332,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H332)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H332)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H332)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H332)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H332)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H332)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H332)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H332)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H332)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H332)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H332)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H332)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H332)),1,0)))</f>
@@ -24229,7 +24229,7 @@
         <v>400</v>
       </c>
       <c r="S332" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T332" s="13">
         <v>331</v>
@@ -24290,7 +24290,7 @@
         <v>400</v>
       </c>
       <c r="S333" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T333" s="13">
         <v>332</v>
@@ -24353,7 +24353,7 @@
         <v>400</v>
       </c>
       <c r="S334" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T334" s="13">
         <v>333</v>
@@ -24378,7 +24378,7 @@
       </c>
       <c r="F335" s="11"/>
       <c r="G335" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H335" s="10" t="s">
         <v>954</v>
@@ -24412,7 +24412,7 @@
         <v>400</v>
       </c>
       <c r="S335" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T335" s="13">
         <v>334</v>
@@ -24439,7 +24439,7 @@
         <v>923</v>
       </c>
       <c r="G336" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H336" s="10" t="s">
         <v>543</v>
@@ -24473,7 +24473,7 @@
         <v>400</v>
       </c>
       <c r="S336" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T336" s="13">
         <v>335</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="F337" s="11"/>
       <c r="G337" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H337" s="10" t="s">
         <v>926</v>
@@ -24534,7 +24534,7 @@
         <v>400</v>
       </c>
       <c r="S337" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T337" s="13">
         <v>336</v>
@@ -24567,7 +24567,7 @@
       <c r="I338" s="10"/>
       <c r="J338" s="10"/>
       <c r="K338" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L338" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H338="",0,LEN(H338)-LEN(SUBSTITUTE(H338,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H338)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H338)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H338)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H338)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H338)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H338)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H338)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H338)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H338)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H338)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H338)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H338)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H338)),1,0)))</f>
@@ -24595,7 +24595,7 @@
         <v>400</v>
       </c>
       <c r="S338" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T338" s="13">
         <v>337</v>
@@ -24620,7 +24620,7 @@
       </c>
       <c r="F339" s="11"/>
       <c r="G339" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H339" s="10" t="s">
         <v>934</v>
@@ -24656,7 +24656,7 @@
         <v>400</v>
       </c>
       <c r="S339" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T339" s="13">
         <v>338</v>
@@ -24681,15 +24681,15 @@
       </c>
       <c r="F340" s="11"/>
       <c r="G340" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H340" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I340" s="10"/>
       <c r="J340" s="10"/>
       <c r="K340" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L340" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H340="",0,LEN(H340)-LEN(SUBSTITUTE(H340,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H340)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H340)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H340)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H340)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H340)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H340)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H340)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H340)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H340)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H340)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H340)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H340)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H340)),1,0)))</f>
@@ -24717,7 +24717,7 @@
         <v>400</v>
       </c>
       <c r="S340" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T340" s="13">
         <v>339</v>
@@ -24742,7 +24742,7 @@
       </c>
       <c r="F341" s="11"/>
       <c r="G341" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H341" s="10" t="s">
         <v>862</v>
@@ -24776,7 +24776,7 @@
         <v>400</v>
       </c>
       <c r="S341" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T341" s="13">
         <v>340</v>
@@ -24809,7 +24809,7 @@
       <c r="I342" s="10"/>
       <c r="J342" s="10"/>
       <c r="K342" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L342" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H342="",0,LEN(H342)-LEN(SUBSTITUTE(H342,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H342)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H342)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H342)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H342)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H342)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H342)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H342)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H342)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H342)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H342)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H342)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H342)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H342)),1,0)))</f>
@@ -24837,7 +24837,7 @@
         <v>400</v>
       </c>
       <c r="S342" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T342" s="13">
         <v>341</v>
@@ -24862,15 +24862,15 @@
       </c>
       <c r="F343" s="11"/>
       <c r="G343" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H343" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I343" s="10"/>
       <c r="J343" s="10"/>
       <c r="K343" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L343" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H343="",0,LEN(H343)-LEN(SUBSTITUTE(H343,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H343)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H343)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H343)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H343)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H343)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H343)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H343)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H343)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H343)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H343)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H343)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H343)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H343)),1,0)))</f>
@@ -24898,7 +24898,7 @@
         <v>400</v>
       </c>
       <c r="S343" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T343" s="13">
         <v>342</v>
@@ -24957,7 +24957,7 @@
         <v>400</v>
       </c>
       <c r="S344" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T344" s="13">
         <v>343</v>
@@ -25018,7 +25018,7 @@
         <v>400</v>
       </c>
       <c r="S345" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T345" s="13">
         <v>344</v>
@@ -25051,7 +25051,7 @@
       <c r="I346" s="10"/>
       <c r="J346" s="10"/>
       <c r="K346" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L346" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H346="",0,LEN(H346)-LEN(SUBSTITUTE(H346,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H346)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H346)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H346)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H346)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H346)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H346)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H346)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H346)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H346)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H346)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H346)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H346)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H346)),1,0)))</f>
@@ -25079,7 +25079,7 @@
         <v>400</v>
       </c>
       <c r="S346" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T346" s="13">
         <v>345</v>
@@ -25138,7 +25138,7 @@
         <v>400</v>
       </c>
       <c r="S347" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T347" s="13">
         <v>346</v>
@@ -25163,7 +25163,7 @@
       </c>
       <c r="F348" s="11"/>
       <c r="G348" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H348" s="10" t="s">
         <v>974</v>
@@ -25197,7 +25197,7 @@
         <v>400</v>
       </c>
       <c r="S348" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T348" s="13">
         <v>347</v>
@@ -25230,7 +25230,7 @@
       <c r="I349" s="10"/>
       <c r="J349" s="10"/>
       <c r="K349" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L349" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H349="",0,LEN(H349)-LEN(SUBSTITUTE(H349,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H349)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H349)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H349)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H349)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H349)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H349)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H349)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H349)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H349)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H349)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H349)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H349)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H349)),1,0)))</f>
@@ -25258,7 +25258,7 @@
         <v>400</v>
       </c>
       <c r="S349" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T349" s="13">
         <v>348</v>
@@ -25283,7 +25283,7 @@
       </c>
       <c r="F350" s="11"/>
       <c r="G350" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H350" s="10" t="s">
         <v>980</v>
@@ -25319,7 +25319,7 @@
         <v>400</v>
       </c>
       <c r="S350" s="8" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="T350" s="13">
         <v>349</v>
@@ -25344,7 +25344,7 @@
       </c>
       <c r="F351" s="11"/>
       <c r="G351" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H351" s="10" t="s">
         <v>478</v>
@@ -25378,7 +25378,7 @@
         <v>400</v>
       </c>
       <c r="S351" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T351" s="13">
         <v>350</v>
@@ -25403,7 +25403,7 @@
       </c>
       <c r="F352" s="11"/>
       <c r="G352" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H352" s="10" t="s">
         <v>986</v>
@@ -25437,7 +25437,7 @@
         <v>400</v>
       </c>
       <c r="S352" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T352" s="13">
         <v>351</v>
@@ -25470,7 +25470,7 @@
       <c r="I353" s="10"/>
       <c r="J353" s="10"/>
       <c r="K353" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L353" s="12">
         <f>计价规则!$B$2+计价规则!$B$3*MAX(0,IF(H353="",0,LEN(H353)-LEN(SUBSTITUTE(H353,"、",""))+1)-(IF(ISNUMBER(SEARCH("WiFi通信模块",H353)),1,0)+IF(ISNUMBER(SEARCH("ESP8266 WiFi模块",H353)),1,0)+IF(ISNUMBER(SEARCH("NRF24L01无线通信模块",H353)),1,0)+IF(ISNUMBER(SEARCH("蓝牙模块",H353)),1,0)+IF(ISNUMBER(SEARCH("语音识别模块",H353)),1,0)+IF(ISNUMBER(SEARCH("语音播报模块",H353)),1,0)+IF(ISNUMBER(SEARCH("RFID模块",H353)),1,0)+IF(ISNUMBER(SEARCH("RFID读卡模块",H353)),1,0)+IF(ISNUMBER(SEARCH("GPS定位模块",H353)),1,0)+IF(ISNUMBER(SEARCH("GSM通信模块",H353)),1,0)+IF(ISNUMBER(SEARCH("摄像头模块",H353)),1,0)+IF(ISNUMBER(SEARCH("人脸识别模块",H353)),1,0)+IF(ISNUMBER(SEARCH("手势识别传感器",H353)),1,0)))</f>
@@ -25498,7 +25498,7 @@
         <v>400</v>
       </c>
       <c r="S353" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T353" s="13">
         <v>352</v>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="F354" s="11"/>
       <c r="G354" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H354" s="10" t="s">
         <v>992</v>
@@ -25557,7 +25557,7 @@
         <v>400</v>
       </c>
       <c r="S354" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T354" s="13">
         <v>353</v>
@@ -25616,7 +25616,7 @@
         <v>400</v>
       </c>
       <c r="S355" s="8" t="s">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="T355" s="13">
         <v>354</v>
@@ -25637,14 +25637,14 @@
         <v>997</v>
       </c>
       <c r="E356" s="11" t="s">
-        <v>998</v>
+        <v>283</v>
       </c>
       <c r="F356" s="11"/>
       <c r="G356" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H356" s="10" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="I356" s="10"/>
       <c r="J356" s="10"/>
@@ -25675,7 +25675,7 @@
         <v>400</v>
       </c>
       <c r="S356" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T356" s="13">
         <v>355</v>
@@ -25690,10 +25690,10 @@
         <v>683</v>
       </c>
       <c r="C357" s="14" t="s">
+        <v>999</v>
+      </c>
+      <c r="D357" s="10" t="s">
         <v>1000</v>
-      </c>
-      <c r="D357" s="10" t="s">
-        <v>1001</v>
       </c>
       <c r="E357" s="11" t="s">
         <v>283</v>
@@ -25703,7 +25703,7 @@
         <v>185</v>
       </c>
       <c r="H357" s="10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I357" s="10"/>
       <c r="J357" s="10"/>
@@ -25734,7 +25734,7 @@
         <v>400</v>
       </c>
       <c r="S357" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T357" s="13">
         <v>356</v>
@@ -25749,10 +25749,10 @@
         <v>683</v>
       </c>
       <c r="C358" s="14" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D358" s="10" t="s">
         <v>1003</v>
-      </c>
-      <c r="D358" s="10" t="s">
-        <v>1004</v>
       </c>
       <c r="E358" s="11" t="s">
         <v>283</v>
@@ -25808,10 +25808,10 @@
         <v>683</v>
       </c>
       <c r="C359" s="14" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D359" s="10" t="s">
         <v>1005</v>
-      </c>
-      <c r="D359" s="10" t="s">
-        <v>1006</v>
       </c>
       <c r="E359" s="11" t="s">
         <v>283</v>
@@ -25864,16 +25864,16 @@
         <v>359</v>
       </c>
       <c r="B360" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C360" s="9" t="s">
         <v>1007</v>
       </c>
-      <c r="C360" s="9" t="s">
+      <c r="D360" s="10" t="s">
         <v>1008</v>
       </c>
-      <c r="D360" s="10" t="s">
+      <c r="E360" s="11" t="s">
         <v>1009</v>
-      </c>
-      <c r="E360" s="11" t="s">
-        <v>998</v>
       </c>
       <c r="F360" s="11"/>
       <c r="G360" s="10" t="s">
@@ -25923,7 +25923,7 @@
         <v>360</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C361" s="9" t="s">
         <v>1011</v>
@@ -25932,11 +25932,11 @@
         <v>1012</v>
       </c>
       <c r="E361" s="11" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="F361" s="11"/>
       <c r="G361" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H361" s="10" t="s">
         <v>1013</v>

--- a/data/项目链接清单.xlsx
+++ b/data/项目链接清单.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="1067">
   <si>
     <t>序号</t>
   </si>
@@ -3094,6 +3094,141 @@
   </si>
   <si>
     <t>全套文档费</t>
+  </si>
+  <si>
+    <t>51单片机的DS12C887万年历农历仿真设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的宠物自动喂食投料控制仿真设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的双路倒车雷达测距报警系统 1</t>
+  </si>
+  <si>
+    <t>基于STM32的六路抢答器仿真 1</t>
+  </si>
+  <si>
+    <t>51单片机交通灯_调绿灯时间+紧急 1</t>
+  </si>
+  <si>
+    <t>TCP7107数字式温度计（纯硬件仿真 无代码） 1</t>
+  </si>
+  <si>
+    <t>51单片机的PWM控制直流电机仿真设计 1</t>
+  </si>
+  <si>
+    <t>STC15单片机交通灯_紧急+夜间模式 1</t>
+  </si>
+  <si>
+    <t>51单片机的电子钟万年历_LCD1602显示 1</t>
+  </si>
+  <si>
+    <t>51单片机音乐盒设计_10首歌 1</t>
+  </si>
+  <si>
+    <t>51单片机热电偶温度报警器_LCD显示 1</t>
+  </si>
+  <si>
+    <t>51单片机HC-SR04超声波测距带温度补偿_倒车雷达 1</t>
+  </si>
+  <si>
+    <t>51单片机的十字路口红绿灯带左转设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的数字电压表0-150V量程设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的电压测量0-5V超范围报警 1</t>
+  </si>
+  <si>
+    <t>51单片机的打地鼠游戏设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的简易汽车雨刮器设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的时钟倒计时设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的防火防盗系统设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的公交车报站系统设计 1</t>
+  </si>
+  <si>
+    <t>51单片简易时钟DS1302四位数码管显示 1</t>
+  </si>
+  <si>
+    <t>51单片机的声控灯 1</t>
+  </si>
+  <si>
+    <t>51单片机呼吸灯 1</t>
+  </si>
+  <si>
+    <t>51单片机电动感应门控制 1</t>
+  </si>
+  <si>
+    <t>51单片机电动窗帘控制OLED显示 1</t>
+  </si>
+  <si>
+    <t>51单片机远程防盗报警器 1</t>
+  </si>
+  <si>
+    <t>51单片机停车场刷卡计费器 1</t>
+  </si>
+  <si>
+    <t>51单片机16X16点阵显示串口数据传输 1</t>
+  </si>
+  <si>
+    <t>51单片机热电偶温度报警器_数码管显示 1</t>
+  </si>
+  <si>
+    <t>51单片机十字路交通灯仿真_黄灯闪烁+夜间+夜间 1</t>
+  </si>
+  <si>
+    <t>51单片机交通信号灯仿真_东西管制+南北管制 1</t>
+  </si>
+  <si>
+    <t>51单片机十字路口交通信号灯_启动+绿灯同亮报警 1</t>
+  </si>
+  <si>
+    <t>51单片机串口交通灯控制器_紧急+夜间+忙闲时+夜间行人模式 1</t>
+  </si>
+  <si>
+    <t>51单片机简易交通灯_5秒黄灯常亮 1</t>
+  </si>
+  <si>
+    <t>51单片机红绿黄交通灯_紧急开关+5s黄灯常亮 1</t>
+  </si>
+  <si>
+    <t>51单片机DS18B20温控风扇 1</t>
+  </si>
+  <si>
+    <t>51单片机手动计步器设计 1</t>
+  </si>
+  <si>
+    <t>51单片机的电子血压温度计(健康监测系统) 1</t>
+  </si>
+  <si>
+    <t>51单片机简易电阻测量仪仿真设计 1</t>
+  </si>
+  <si>
+    <t>51单片机自行车测速里程码表设计 1</t>
+  </si>
+  <si>
+    <t>51单片机正负5V电压表仿真设计 1</t>
+  </si>
+  <si>
+    <t>51单片机八键电子琴设计 1</t>
+  </si>
+  <si>
+    <t>51单片机4位抢答器 1</t>
+  </si>
+  <si>
+    <t>51单片机8位竞赛抢答器_倒计时可调 1</t>
+  </si>
+  <si>
+    <t>51单片机16位抢答器 1</t>
   </si>
 </sst>
 </file>
@@ -4655,7 +4790,7 @@
         <v>35</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>36</v>
+        <v>1033</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>23</v>
@@ -4696,7 +4831,7 @@
         <v>400</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T5" s="13">
         <v>4</v>
@@ -5186,7 +5321,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>69</v>
+        <v>1034</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>23</v>
@@ -5227,7 +5362,7 @@
         <v>400</v>
       </c>
       <c r="S14" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T14" s="13">
         <v>13</v>
@@ -5363,7 +5498,7 @@
         <v>80</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>81</v>
+        <v>1035</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>23</v>
@@ -5404,7 +5539,7 @@
         <v>400</v>
       </c>
       <c r="S17" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T17" s="13">
         <v>16</v>
@@ -5422,7 +5557,7 @@
         <v>84</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>85</v>
+        <v>1036</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>23</v>
@@ -5463,7 +5598,7 @@
         <v>400</v>
       </c>
       <c r="S18" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T18" s="13">
         <v>17</v>
@@ -5481,7 +5616,7 @@
         <v>88</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>89</v>
+        <v>1037</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>23</v>
@@ -5522,7 +5657,7 @@
         <v>400</v>
       </c>
       <c r="S19" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T19" s="13">
         <v>18</v>
@@ -5540,7 +5675,7 @@
         <v>90</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>91</v>
+        <v>1038</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>23</v>
@@ -5581,7 +5716,7 @@
         <v>400</v>
       </c>
       <c r="S20" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T20" s="13">
         <v>19</v>
@@ -5599,7 +5734,7 @@
         <v>93</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>94</v>
+        <v>1039</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>23</v>
@@ -5640,7 +5775,7 @@
         <v>400</v>
       </c>
       <c r="S21" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T21" s="13">
         <v>20</v>
@@ -5658,7 +5793,7 @@
         <v>96</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>97</v>
+        <v>1040</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>23</v>
@@ -5699,7 +5834,7 @@
         <v>400</v>
       </c>
       <c r="S22" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T22" s="13">
         <v>21</v>
@@ -5717,7 +5852,7 @@
         <v>99</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>100</v>
+        <v>1041</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>23</v>
@@ -5760,7 +5895,7 @@
         <v>400</v>
       </c>
       <c r="S23" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T23" s="13">
         <v>22</v>
@@ -5778,7 +5913,7 @@
         <v>103</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>104</v>
+        <v>1042</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>23</v>
@@ -5819,7 +5954,7 @@
         <v>400</v>
       </c>
       <c r="S24" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T24" s="13">
         <v>23</v>
@@ -5837,7 +5972,7 @@
         <v>105</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>106</v>
+        <v>1043</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>23</v>
@@ -5878,7 +6013,7 @@
         <v>400</v>
       </c>
       <c r="S25" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T25" s="13">
         <v>24</v>
@@ -5896,7 +6031,7 @@
         <v>108</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>109</v>
+        <v>1044</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>23</v>
@@ -5937,7 +6072,7 @@
         <v>400</v>
       </c>
       <c r="S26" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T26" s="13">
         <v>25</v>
@@ -5955,7 +6090,7 @@
         <v>110</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>111</v>
+        <v>1045</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>23</v>
@@ -5996,7 +6131,7 @@
         <v>400</v>
       </c>
       <c r="S27" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T27" s="13">
         <v>26</v>
@@ -6014,7 +6149,7 @@
         <v>113</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>114</v>
+        <v>1046</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>23</v>
@@ -6055,7 +6190,7 @@
         <v>400</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T28" s="13">
         <v>27</v>
@@ -6073,7 +6208,7 @@
         <v>117</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>118</v>
+        <v>1047</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>23</v>
@@ -6116,7 +6251,7 @@
         <v>400</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T29" s="13">
         <v>28</v>
@@ -6134,7 +6269,7 @@
         <v>122</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>123</v>
+        <v>1024</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>23</v>
@@ -6175,7 +6310,7 @@
         <v>400</v>
       </c>
       <c r="S30" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T30" s="13">
         <v>29</v>
@@ -6193,7 +6328,7 @@
         <v>126</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>127</v>
+        <v>1048</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>23</v>
@@ -6236,7 +6371,7 @@
         <v>400</v>
       </c>
       <c r="S31" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T31" s="13">
         <v>30</v>
@@ -6254,7 +6389,7 @@
         <v>130</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>131</v>
+        <v>1031</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>23</v>
@@ -6295,7 +6430,7 @@
         <v>400</v>
       </c>
       <c r="S32" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T32" s="13">
         <v>31</v>
@@ -6313,7 +6448,7 @@
         <v>134</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>135</v>
+        <v>1049</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>23</v>
@@ -6354,7 +6489,7 @@
         <v>400</v>
       </c>
       <c r="S33" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T33" s="13">
         <v>32</v>
@@ -6372,7 +6507,7 @@
         <v>137</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>138</v>
+        <v>1050</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>23</v>
@@ -6413,7 +6548,7 @@
         <v>400</v>
       </c>
       <c r="S34" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T34" s="13">
         <v>33</v>
@@ -6431,7 +6566,7 @@
         <v>141</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>142</v>
+        <v>1032</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>23</v>
@@ -6472,7 +6607,7 @@
         <v>400</v>
       </c>
       <c r="S35" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T35" s="13">
         <v>34</v>
@@ -7729,7 +7864,7 @@
         <v>209</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>210</v>
+        <v>1026</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>23</v>
@@ -7770,7 +7905,7 @@
         <v>400</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T57" s="13">
         <v>56</v>
@@ -7847,7 +7982,7 @@
         <v>215</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>216</v>
+        <v>1051</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>23</v>
@@ -7888,7 +8023,7 @@
         <v>400</v>
       </c>
       <c r="S59" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T59" s="13">
         <v>58</v>
@@ -7906,7 +8041,7 @@
         <v>218</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>219</v>
+        <v>1052</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>23</v>
@@ -7947,7 +8082,7 @@
         <v>400</v>
       </c>
       <c r="S60" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T60" s="13">
         <v>59</v>
@@ -8496,7 +8631,7 @@
         <v>242</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>243</v>
+        <v>1053</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>23</v>
@@ -8537,7 +8672,7 @@
         <v>400</v>
       </c>
       <c r="S70" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T70" s="13">
         <v>69</v>
@@ -8850,7 +8985,7 @@
         <v>255</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>256</v>
+        <v>1054</v>
       </c>
       <c r="E76" s="11" t="s">
         <v>23</v>
@@ -8891,7 +9026,7 @@
         <v>400</v>
       </c>
       <c r="S76" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T76" s="13">
         <v>75</v>
@@ -9145,7 +9280,7 @@
         <v>268</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>269</v>
+        <v>1055</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>23</v>
@@ -9186,7 +9321,7 @@
         <v>400</v>
       </c>
       <c r="S81" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T81" s="13">
         <v>80</v>
@@ -9263,7 +9398,7 @@
         <v>272</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>273</v>
+        <v>1056</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>23</v>
@@ -9304,7 +9439,7 @@
         <v>400</v>
       </c>
       <c r="S83" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T83" s="13">
         <v>82</v>
@@ -9617,7 +9752,7 @@
         <v>286</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>287</v>
+        <v>1029</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>23</v>
@@ -9660,7 +9795,7 @@
         <v>400</v>
       </c>
       <c r="S89" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T89" s="13">
         <v>88</v>
@@ -10331,7 +10466,7 @@
         <v>321</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>322</v>
+        <v>1057</v>
       </c>
       <c r="E101" s="11" t="s">
         <v>23</v>
@@ -10372,7 +10507,7 @@
         <v>400</v>
       </c>
       <c r="S101" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T101" s="13">
         <v>100</v>
@@ -10862,7 +10997,7 @@
         <v>346</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>347</v>
+        <v>1027</v>
       </c>
       <c r="E110" s="11" t="s">
         <v>23</v>
@@ -10903,7 +11038,7 @@
         <v>400</v>
       </c>
       <c r="S110" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T110" s="13">
         <v>109</v>
@@ -10921,7 +11056,7 @@
         <v>349</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>350</v>
+        <v>1058</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>23</v>
@@ -10962,7 +11097,7 @@
         <v>400</v>
       </c>
       <c r="S111" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T111" s="13">
         <v>110</v>
@@ -11216,7 +11351,7 @@
         <v>364</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>365</v>
+        <v>1059</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>23</v>
@@ -11257,7 +11392,7 @@
         <v>400</v>
       </c>
       <c r="S116" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T116" s="13">
         <v>115</v>
@@ -11334,7 +11469,7 @@
         <v>371</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>372</v>
+        <v>1022</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>23</v>
@@ -11375,7 +11510,7 @@
         <v>400</v>
       </c>
       <c r="S118" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T118" s="13">
         <v>117</v>
@@ -11393,7 +11528,7 @@
         <v>373</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>374</v>
+        <v>1023</v>
       </c>
       <c r="E119" s="11" t="s">
         <v>23</v>
@@ -11434,7 +11569,7 @@
         <v>400</v>
       </c>
       <c r="S119" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T119" s="13">
         <v>118</v>
@@ -11511,7 +11646,7 @@
         <v>378</v>
       </c>
       <c r="D121" s="10" t="s">
-        <v>379</v>
+        <v>1028</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>23</v>
@@ -11552,7 +11687,7 @@
         <v>400</v>
       </c>
       <c r="S121" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T121" s="13">
         <v>120</v>
@@ -11865,7 +12000,7 @@
         <v>394</v>
       </c>
       <c r="D127" s="10" t="s">
-        <v>395</v>
+        <v>1060</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>23</v>
@@ -11906,7 +12041,7 @@
         <v>400</v>
       </c>
       <c r="S127" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T127" s="13">
         <v>126</v>
@@ -14284,7 +14419,7 @@
         <v>508</v>
       </c>
       <c r="D168" s="10" t="s">
-        <v>509</v>
+        <v>1061</v>
       </c>
       <c r="E168" s="11" t="s">
         <v>23</v>
@@ -14325,7 +14460,7 @@
         <v>400</v>
       </c>
       <c r="S168" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T168" s="13">
         <v>167</v>
@@ -15641,7 +15776,7 @@
         <v>572</v>
       </c>
       <c r="D191" s="10" t="s">
-        <v>573</v>
+        <v>1062</v>
       </c>
       <c r="E191" s="11" t="s">
         <v>23</v>
@@ -15682,7 +15817,7 @@
         <v>400</v>
       </c>
       <c r="S191" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T191" s="13">
         <v>190</v>
@@ -15700,7 +15835,7 @@
         <v>574</v>
       </c>
       <c r="D192" s="10" t="s">
-        <v>575</v>
+        <v>1063</v>
       </c>
       <c r="E192" s="11" t="s">
         <v>23</v>
@@ -15741,7 +15876,7 @@
         <v>400</v>
       </c>
       <c r="S192" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T192" s="13">
         <v>191</v>
@@ -16233,7 +16368,7 @@
         <v>601</v>
       </c>
       <c r="D201" s="10" t="s">
-        <v>602</v>
+        <v>1030</v>
       </c>
       <c r="E201" s="11" t="s">
         <v>23</v>
@@ -16274,7 +16409,7 @@
         <v>400</v>
       </c>
       <c r="S201" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T201" s="13">
         <v>200</v>
@@ -17826,7 +17961,7 @@
         <v>665</v>
       </c>
       <c r="D228" s="10" t="s">
-        <v>666</v>
+        <v>1064</v>
       </c>
       <c r="E228" s="11" t="s">
         <v>23</v>
@@ -17867,7 +18002,7 @@
         <v>400</v>
       </c>
       <c r="S228" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T228" s="13">
         <v>227</v>
@@ -18003,7 +18138,7 @@
         <v>671</v>
       </c>
       <c r="D231" s="10" t="s">
-        <v>672</v>
+        <v>1065</v>
       </c>
       <c r="E231" s="11" t="s">
         <v>23</v>
@@ -18044,7 +18179,7 @@
         <v>400</v>
       </c>
       <c r="S231" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T231" s="13">
         <v>230</v>
@@ -18298,7 +18433,7 @@
         <v>681</v>
       </c>
       <c r="D236" s="10" t="s">
-        <v>682</v>
+        <v>1066</v>
       </c>
       <c r="E236" s="11" t="s">
         <v>23</v>
@@ -18339,7 +18474,7 @@
         <v>400</v>
       </c>
       <c r="S236" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T236" s="13">
         <v>235</v>
@@ -25752,7 +25887,7 @@
         <v>1002</v>
       </c>
       <c r="D358" s="10" t="s">
-        <v>1003</v>
+        <v>1025</v>
       </c>
       <c r="E358" s="11" t="s">
         <v>283</v>
@@ -25793,7 +25928,7 @@
         <v>400</v>
       </c>
       <c r="S358" s="8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T358" s="13">
         <v>357</v>
